--- a/results/climate_change_breakdown/2025/propanol production, biogas, green ethylene_GLO.xlsx
+++ b/results/climate_change_breakdown/2025/propanol production, biogas, green ethylene_GLO.xlsx
@@ -444,7 +444,7 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>-0.4668798218518913</v>
+        <v>-0.4982176601162264</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>9</v>
       </c>
       <c r="D7">
-        <v>0.03322661175763537</v>
+        <v>0.002115668043832193</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -546,7 +546,7 @@
         <v>10</v>
       </c>
       <c r="D8">
-        <v>0.0001706406416039289</v>
+        <v>4.90142751400416E-06</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -563,7 +563,7 @@
         <v>11</v>
       </c>
       <c r="D9">
-        <v>6.365857832198448E-05</v>
+        <v>2.502196104277235E-06</v>
       </c>
       <c r="E9">
         <v>1</v>
